--- a/alignment_flat_standoffs.xlsx
+++ b/alignment_flat_standoffs.xlsx
@@ -1,75 +1,188 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://office365stanford-my.sharepoint.com/personal/rscott0_stanford_edu/Documents/SU26/UV Laser Singulation/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="11" documentId="11_6A427DE7D64704DE6A34E8954E11AEF8BB4D8F62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4D34386-C289-4C29-9B4C-F8EC8DE3CBEA}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat standoffs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Flat standoffs" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+  <si>
+    <t>Alignment-line standoffs from wafer flats (100 mm wafer)</t>
+  </si>
+  <si>
+    <t>Standoff = center of the scribed line to the wafer edge at that flat. The bottom (horizontal) line reads the major/primary flat (-Y); the left (vertical) line reads the minor/secondary flat (-X). Top and right lines sit on the plain arc (not flat-referenced). Fill the yellow measured cells during a calibration run; Delta = measured - nominal is the raw per-axis offset.</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>Line (um x mm)</t>
+  </si>
+  <si>
+    <t>Major line y (mm)</t>
+  </si>
+  <si>
+    <t>Major standoff (mm)</t>
+  </si>
+  <si>
+    <t>Major measured (mm)</t>
+  </si>
+  <si>
+    <t>Major Δ (mm)</t>
+  </si>
+  <si>
+    <t>Minor line x (mm)</t>
+  </si>
+  <si>
+    <t>Minor standoff (mm)</t>
+  </si>
+  <si>
+    <t>Minor measured (mm)</t>
+  </si>
+  <si>
+    <t>Minor Δ (mm)</t>
+  </si>
+  <si>
+    <t>v1</t>
+  </si>
+  <si>
+    <t>50 x 5</t>
+  </si>
+  <si>
+    <t>v2</t>
+  </si>
+  <si>
+    <t>20 x 10</t>
+  </si>
+  <si>
+    <t>v3</t>
+  </si>
+  <si>
+    <t>50 x 10</t>
+  </si>
+  <si>
+    <t>Reference geometry (100 mm wafer)</t>
+  </si>
+  <si>
+    <t>Wafer radius (mm)</t>
+  </si>
+  <si>
+    <t>Major (primary) flat length (mm), faces -Y</t>
+  </si>
+  <si>
+    <t>Minor (secondary) flat length (mm), faces -X</t>
+  </si>
+  <si>
+    <t>Major flat edge, y (mm) = -sqrt(R^2-(major/2)^2)</t>
+  </si>
+  <si>
+    <t>Minor flat edge, x (mm) = -sqrt(R^2-(minor/2)^2)</t>
+  </si>
+  <si>
+    <t>Legend: blue = fixed design values; yellow = fill during the calibration run; Delta computes automatically.</t>
+  </si>
+  <si>
+    <t>Standoff = nominal line center minus the flat edge (positive = line sits inboard of the flat).</t>
+  </si>
+  <si>
+    <t>Example: if v1's major line measures 17.45 mm off the flat, Major Delta = +0.164 mm.</t>
+  </si>
+  <si>
+    <t>Delta (measured - nominal) is the raw per-axis shift; apply it per your GLOBAL_X/Y_OFFSET_UM sign convention in python/split_klayout.py.</t>
+  </si>
+  <si>
+    <t>Arc-side lines (not flat-referenced): v1 +-40 / +-30, v2 right x=+42 / top y=+32, v3 +-37 / +-27.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000"/>
-    <numFmt numFmtId="165" formatCode="+0.000;-0.000;0.000"/>
+    <numFmt numFmtId="165" formatCode="\+0.000;\-0.000;0.000"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <b val="1"/>
+      <b/>
       <sz val="14"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-    </font>
-    <font>
       <name val="Arial"/>
     </font>
     <font>
+      <i/>
+      <sz val="9"/>
       <name val="Arial"/>
-      <color rgb="000000FF"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor rgb="FFD9E1F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -83,114 +196,57 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </left>
       <right style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </right>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="15">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -478,284 +534,252 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col min="1" max="1" width="7" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+    <col min="8" max="9" width="16" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Alignment-line standoffs from wafer flats (100 mm wafer)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="46" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Standoff = center of the scribed line to the wafer edge at that flat. The bottom (horizontal) line reads the major/primary flat (-Y); the left (vertical) line reads the minor/secondary flat (-X). Top and right lines sit on the plain arc (not flat-referenced). Fill the yellow measured cells during a calibration run; Delta = measured - nominal is the raw per-axis offset.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Line (um x mm)</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Major line y (mm)</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Major standoff (mm)</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Major measured (mm)</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Major Δ (mm)</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Minor line x (mm)</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>Minor standoff (mm)</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>Minor measured (mm)</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>Minor Δ (mm)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>v1</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>50 x 5</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="n">
+    <row r="1" spans="1:10" ht="17.649999999999999" x14ac:dyDescent="0.5">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+    </row>
+    <row r="2" spans="1:10" ht="46.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+    </row>
+    <row r="4" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="4">
         <v>-30</v>
       </c>
-      <c r="D5" s="7" t="n">
-        <v>17.286</v>
-      </c>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="9">
+      <c r="D5" s="5">
+        <v>17.286000000000001</v>
+      </c>
+      <c r="E5" s="6">
+        <f>(17.09+16.03)/2</f>
+        <v>16.560000000000002</v>
+      </c>
+      <c r="F5" s="7">
         <f>IF(E5="","",E5-D5)</f>
-        <v/>
-      </c>
-      <c r="G5" s="6" t="n">
+        <v>-0.72599999999999909</v>
+      </c>
+      <c r="G5" s="4">
         <v>-40</v>
       </c>
-      <c r="H5" s="7" t="n">
-        <v>9.183</v>
-      </c>
-      <c r="I5" s="8" t="n"/>
-      <c r="J5" s="9">
+      <c r="H5" s="5">
+        <v>9.1829999999999998</v>
+      </c>
+      <c r="I5" s="6">
+        <v>8.98</v>
+      </c>
+      <c r="J5" s="7">
         <f>IF(I5="","",I5-H5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>v2</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>20 x 10</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>-42.286</v>
-      </c>
-      <c r="D6" s="7" t="n">
+        <v>-0.2029999999999994</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="4">
+        <v>-42.286000000000001</v>
+      </c>
+      <c r="D6" s="5">
         <v>5</v>
       </c>
-      <c r="E6" s="8" t="n"/>
-      <c r="F6" s="9">
+      <c r="E6" s="6">
+        <v>4.45</v>
+      </c>
+      <c r="F6" s="7">
         <f>IF(E6="","",E6-D6)</f>
-        <v/>
-      </c>
-      <c r="G6" s="6" t="n">
+        <v>-0.54999999999999982</v>
+      </c>
+      <c r="G6" s="4">
         <v>-44.183</v>
       </c>
-      <c r="H6" s="7" t="n">
+      <c r="H6" s="5">
         <v>5</v>
       </c>
-      <c r="I6" s="8" t="n"/>
-      <c r="J6" s="9">
+      <c r="I6" s="6">
+        <v>4.82</v>
+      </c>
+      <c r="J6" s="7">
         <f>IF(I6="","",I6-H6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>v3</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>50 x 10</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="n">
+        <v>-0.17999999999999972</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="4">
         <v>-27</v>
       </c>
-      <c r="D7" s="7" t="n">
-        <v>20.286</v>
-      </c>
-      <c r="E7" s="8" t="n"/>
-      <c r="F7" s="9">
+      <c r="D7" s="5">
+        <v>20.286000000000001</v>
+      </c>
+      <c r="E7" s="6">
+        <f>(20.08+19.84)/2</f>
+        <v>19.96</v>
+      </c>
+      <c r="F7" s="7">
         <f>IF(E7="","",E7-D7)</f>
-        <v/>
-      </c>
-      <c r="G7" s="6" t="n">
+        <v>-0.32600000000000051</v>
+      </c>
+      <c r="G7" s="4">
         <v>-37</v>
       </c>
-      <c r="H7" s="7" t="n">
+      <c r="H7" s="5">
         <v>12.183</v>
       </c>
-      <c r="I7" s="8" t="n"/>
-      <c r="J7" s="9">
+      <c r="I7" s="6">
+        <v>12.01</v>
+      </c>
+      <c r="J7" s="7">
         <f>IF(I7="","",I7-H7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>Reference geometry (100 mm wafer)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="inlineStr">
-        <is>
-          <t>Wafer radius (mm)</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="n">
+        <v>-0.17300000000000004</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A9" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A10" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="10">
         <v>50</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>Major (primary) flat length (mm), faces -Y</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="n">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A11" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="10">
         <v>32.5</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>Minor (secondary) flat length (mm), faces -X</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="n">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A12" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="10">
         <v>18</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>Major flat edge, y (mm) = -sqrt(R^2-(major/2)^2)</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="n">
-        <v>-47.286</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>Minor flat edge, x (mm) = -sqrt(R^2-(minor/2)^2)</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="n">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A13" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="10">
+        <v>-47.286000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A14" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="10">
         <v>-49.183</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>Legend: blue = fixed design values; yellow = fill during the calibration run; Delta computes automatically.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="13" t="inlineStr">
-        <is>
-          <t>Standoff = nominal line center minus the flat edge (positive = line sits inboard of the flat).</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>Example: if v1's major line measures 17.45 mm off the flat, Major Delta = +0.164 mm.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t>Delta (measured - nominal) is the raw per-axis shift; apply it per your GLOBAL_X/Y_OFFSET_UM sign convention in python/split_klayout.py.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="13" t="inlineStr">
-        <is>
-          <t>Arc-side lines (not flat-referenced): v1 +-40 / +-30, v2 right x=+42 / top y=+32, v3 +-37 / +-27.</t>
-        </is>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A16" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A17" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A18" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A19" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A20" s="11" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
